--- a/data/harvest_species_list_characteristics_5.xlsx
+++ b/data/harvest_species_list_characteristics_5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariegutgesell/Desktop/Wild Foods Repo/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariegutgesell/LocalRepos/Wild Foods Repo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00230C8-DEAA-C44F-A41A-41D5CAA131A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEB75F8-BCBB-FE4D-99D5-90A4856FF389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16600" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="28800" windowHeight="16600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T_harvest_species_list" sheetId="1" r:id="rId1"/>
@@ -63551,7 +63551,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650C6DC7-E293-444D-8EA8-E55F354E543B}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:X417"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16"/>
   <cols>
@@ -63632,7 +63631,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="2" spans="1:24" hidden="1">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
         <v>110</v>
       </c>
@@ -63688,7 +63687,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="3" spans="1:24" hidden="1">
+    <row r="3" spans="1:24">
       <c r="A3" t="s">
         <v>110</v>
       </c>
@@ -63741,7 +63740,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:24" hidden="1">
+    <row r="4" spans="1:24">
       <c r="A4" t="s">
         <v>110</v>
       </c>
@@ -63794,7 +63793,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="1:24" hidden="1">
+    <row r="5" spans="1:24">
       <c r="A5" t="s">
         <v>110</v>
       </c>
@@ -63850,7 +63849,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="6" spans="1:24" hidden="1">
+    <row r="6" spans="1:24">
       <c r="A6" t="s">
         <v>110</v>
       </c>
@@ -63903,7 +63902,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="7" spans="1:24" hidden="1">
+    <row r="7" spans="1:24">
       <c r="A7" t="s">
         <v>110</v>
       </c>
@@ -63956,7 +63955,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:24" hidden="1">
+    <row r="8" spans="1:24">
       <c r="A8" t="s">
         <v>110</v>
       </c>
@@ -64009,7 +64008,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="9" spans="1:24" hidden="1">
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -64062,7 +64061,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:24" hidden="1">
+    <row r="10" spans="1:24">
       <c r="A10" t="s">
         <v>110</v>
       </c>
@@ -64115,7 +64114,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="11" spans="1:24" hidden="1">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -64165,7 +64164,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="12" spans="1:24" hidden="1">
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
         <v>110</v>
       </c>
@@ -64215,7 +64214,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="13" spans="1:24" hidden="1">
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>110</v>
       </c>
@@ -64265,7 +64264,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="14" spans="1:24" hidden="1">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>110</v>
       </c>
@@ -64315,7 +64314,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="15" spans="1:24" hidden="1">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>110</v>
       </c>
@@ -64365,7 +64364,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="16" spans="1:24" hidden="1">
+    <row r="16" spans="1:24">
       <c r="A16" t="s">
         <v>110</v>
       </c>
@@ -64415,7 +64414,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
         <v>110</v>
       </c>
@@ -64468,7 +64467,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1">
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
         <v>110</v>
       </c>
@@ -64521,7 +64520,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1">
+    <row r="19" spans="1:19">
       <c r="A19" t="s">
         <v>110</v>
       </c>
@@ -64574,7 +64573,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1">
+    <row r="20" spans="1:19">
       <c r="A20" t="s">
         <v>110</v>
       </c>
@@ -64627,7 +64626,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1">
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -64680,7 +64679,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1">
+    <row r="22" spans="1:19">
       <c r="A22" t="s">
         <v>110</v>
       </c>
@@ -64733,7 +64732,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1">
+    <row r="23" spans="1:19">
       <c r="A23" t="s">
         <v>110</v>
       </c>
@@ -64786,7 +64785,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1">
+    <row r="24" spans="1:19">
       <c r="A24" t="s">
         <v>110</v>
       </c>
@@ -64839,7 +64838,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1">
+    <row r="25" spans="1:19">
       <c r="A25" t="s">
         <v>110</v>
       </c>
@@ -64892,7 +64891,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1">
+    <row r="26" spans="1:19">
       <c r="A26" t="s">
         <v>110</v>
       </c>
@@ -64942,7 +64941,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="27" spans="1:19" hidden="1">
+    <row r="27" spans="1:19">
       <c r="A27" t="s">
         <v>110</v>
       </c>
@@ -64995,7 +64994,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="28" spans="1:19" hidden="1">
+    <row r="28" spans="1:19">
       <c r="A28" t="s">
         <v>110</v>
       </c>
@@ -65048,7 +65047,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="29" spans="1:19" hidden="1">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -65101,7 +65100,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="30" spans="1:19" hidden="1">
+    <row r="30" spans="1:19">
       <c r="A30" t="s">
         <v>110</v>
       </c>
@@ -65151,7 +65150,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="31" spans="1:19" hidden="1">
+    <row r="31" spans="1:19">
       <c r="A31" t="s">
         <v>110</v>
       </c>
@@ -65204,7 +65203,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
         <v>110</v>
       </c>
@@ -65257,7 +65256,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="33" spans="1:19" hidden="1">
+    <row r="33" spans="1:19">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -65310,7 +65309,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="34" spans="1:19" hidden="1">
+    <row r="34" spans="1:19">
       <c r="A34" t="s">
         <v>110</v>
       </c>
@@ -65366,7 +65365,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="1:19" hidden="1">
+    <row r="35" spans="1:19">
       <c r="A35" t="s">
         <v>110</v>
       </c>
@@ -65422,7 +65421,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="36" spans="1:19" hidden="1">
+    <row r="36" spans="1:19">
       <c r="A36" t="s">
         <v>110</v>
       </c>
@@ -65472,7 +65471,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="37" spans="1:19" hidden="1">
+    <row r="37" spans="1:19">
       <c r="A37" t="s">
         <v>110</v>
       </c>
@@ -65522,7 +65521,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="38" spans="1:19" hidden="1">
+    <row r="38" spans="1:19">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -65575,7 +65574,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="39" spans="1:19" hidden="1">
+    <row r="39" spans="1:19">
       <c r="A39" t="s">
         <v>110</v>
       </c>
@@ -65628,7 +65627,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="40" spans="1:19" hidden="1">
+    <row r="40" spans="1:19">
       <c r="A40" t="s">
         <v>110</v>
       </c>
@@ -65681,7 +65680,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="41" spans="1:19" hidden="1">
+    <row r="41" spans="1:19">
       <c r="A41" t="s">
         <v>110</v>
       </c>
@@ -65734,7 +65733,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="42" spans="1:19" hidden="1">
+    <row r="42" spans="1:19">
       <c r="A42" t="s">
         <v>110</v>
       </c>
@@ -65787,7 +65786,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="43" spans="1:19" hidden="1">
+    <row r="43" spans="1:19">
       <c r="A43" t="s">
         <v>110</v>
       </c>
@@ -65840,7 +65839,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="1:19" hidden="1">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
         <v>110</v>
       </c>
@@ -65893,7 +65892,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="45" spans="1:19" hidden="1">
+    <row r="45" spans="1:19">
       <c r="A45" t="s">
         <v>110</v>
       </c>
@@ -65946,7 +65945,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="46" spans="1:19" hidden="1">
+    <row r="46" spans="1:19">
       <c r="A46" t="s">
         <v>110</v>
       </c>
@@ -65999,7 +65998,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="47" spans="1:19" hidden="1">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
         <v>110</v>
       </c>
@@ -66052,7 +66051,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="48" spans="1:19" hidden="1">
+    <row r="48" spans="1:19">
       <c r="A48" t="s">
         <v>110</v>
       </c>
@@ -66102,7 +66101,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="49" spans="1:22" hidden="1">
+    <row r="49" spans="1:22">
       <c r="A49" t="s">
         <v>110</v>
       </c>
@@ -66152,7 +66151,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="50" spans="1:22" hidden="1">
+    <row r="50" spans="1:22">
       <c r="A50" t="s">
         <v>110</v>
       </c>
@@ -66202,7 +66201,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="51" spans="1:22" hidden="1">
+    <row r="51" spans="1:22">
       <c r="A51" t="s">
         <v>110</v>
       </c>
@@ -66252,7 +66251,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="52" spans="1:22" hidden="1">
+    <row r="52" spans="1:22">
       <c r="A52" t="s">
         <v>110</v>
       </c>
@@ -66302,7 +66301,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="53" spans="1:22" hidden="1">
+    <row r="53" spans="1:22">
       <c r="A53" t="s">
         <v>110</v>
       </c>
@@ -66352,7 +66351,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="54" spans="1:22" hidden="1">
+    <row r="54" spans="1:22">
       <c r="A54" t="s">
         <v>110</v>
       </c>
@@ -66402,7 +66401,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="55" spans="1:22" hidden="1">
+    <row r="55" spans="1:22">
       <c r="A55" t="s">
         <v>110</v>
       </c>
@@ -66452,7 +66451,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="56" spans="1:22" hidden="1">
+    <row r="56" spans="1:22">
       <c r="A56" t="s">
         <v>110</v>
       </c>
@@ -66502,7 +66501,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="57" spans="1:22" hidden="1">
+    <row r="57" spans="1:22">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -66552,7 +66551,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="58" spans="1:22" hidden="1">
+    <row r="58" spans="1:22">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -66602,7 +66601,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="59" spans="1:22" hidden="1">
+    <row r="59" spans="1:22">
       <c r="A59" t="s">
         <v>110</v>
       </c>
@@ -66655,7 +66654,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="60" spans="1:22" hidden="1">
+    <row r="60" spans="1:22">
       <c r="A60" t="s">
         <v>110</v>
       </c>
@@ -66705,7 +66704,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="61" spans="1:22" hidden="1">
+    <row r="61" spans="1:22">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -66755,7 +66754,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="62" spans="1:22" hidden="1">
+    <row r="62" spans="1:22">
       <c r="A62" t="s">
         <v>110</v>
       </c>
@@ -66802,7 +66801,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="63" spans="1:22" hidden="1">
+    <row r="63" spans="1:22">
       <c r="A63" t="s">
         <v>110</v>
       </c>
@@ -66849,7 +66848,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="64" spans="1:22" hidden="1">
+    <row r="64" spans="1:22">
       <c r="A64" t="s">
         <v>110</v>
       </c>
@@ -66896,7 +66895,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="65" spans="1:20" hidden="1">
+    <row r="65" spans="1:20">
       <c r="A65" t="s">
         <v>110</v>
       </c>
@@ -66943,7 +66942,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="66" spans="1:20" hidden="1">
+    <row r="66" spans="1:20">
       <c r="A66" t="s">
         <v>110</v>
       </c>
@@ -66993,7 +66992,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="67" spans="1:20" hidden="1">
+    <row r="67" spans="1:20">
       <c r="A67" t="s">
         <v>110</v>
       </c>
@@ -67037,7 +67036,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="68" spans="1:20" hidden="1">
+    <row r="68" spans="1:20">
       <c r="A68" t="s">
         <v>110</v>
       </c>
@@ -67081,7 +67080,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="69" spans="1:20" hidden="1">
+    <row r="69" spans="1:20">
       <c r="A69" t="s">
         <v>110</v>
       </c>
@@ -67128,7 +67127,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="70" spans="1:20" hidden="1">
+    <row r="70" spans="1:20">
       <c r="A70" t="s">
         <v>110</v>
       </c>
@@ -67172,7 +67171,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="71" spans="1:20" hidden="1">
+    <row r="71" spans="1:20">
       <c r="A71" t="s">
         <v>110</v>
       </c>
@@ -67216,7 +67215,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="72" spans="1:20" hidden="1">
+    <row r="72" spans="1:20">
       <c r="A72" t="s">
         <v>110</v>
       </c>
@@ -67263,7 +67262,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="73" spans="1:20" hidden="1">
+    <row r="73" spans="1:20">
       <c r="A73" t="s">
         <v>110</v>
       </c>
@@ -67307,7 +67306,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="74" spans="1:20" hidden="1">
+    <row r="74" spans="1:20">
       <c r="A74" t="s">
         <v>110</v>
       </c>
@@ -67354,7 +67353,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="75" spans="1:20" hidden="1">
+    <row r="75" spans="1:20">
       <c r="A75" t="s">
         <v>110</v>
       </c>
@@ -67401,7 +67400,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="76" spans="1:20" hidden="1">
+    <row r="76" spans="1:20">
       <c r="A76" t="s">
         <v>110</v>
       </c>
@@ -67448,7 +67447,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="77" spans="1:20" hidden="1">
+    <row r="77" spans="1:20">
       <c r="A77" t="s">
         <v>110</v>
       </c>
@@ -67495,7 +67494,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="78" spans="1:20" hidden="1">
+    <row r="78" spans="1:20">
       <c r="A78" t="s">
         <v>110</v>
       </c>
@@ -67542,7 +67541,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="79" spans="1:20" hidden="1">
+    <row r="79" spans="1:20">
       <c r="A79" t="s">
         <v>110</v>
       </c>
@@ -67589,7 +67588,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="80" spans="1:20" hidden="1">
+    <row r="80" spans="1:20">
       <c r="A80" t="s">
         <v>110</v>
       </c>
@@ -67636,7 +67635,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="81" spans="1:19" hidden="1">
+    <row r="81" spans="1:19">
       <c r="A81" t="s">
         <v>110</v>
       </c>
@@ -67683,7 +67682,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="82" spans="1:19" hidden="1">
+    <row r="82" spans="1:19">
       <c r="A82" t="s">
         <v>110</v>
       </c>
@@ -67730,7 +67729,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="83" spans="1:19" hidden="1">
+    <row r="83" spans="1:19">
       <c r="A83" t="s">
         <v>110</v>
       </c>
@@ -67774,7 +67773,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="84" spans="1:19" hidden="1">
+    <row r="84" spans="1:19">
       <c r="A84" t="s">
         <v>110</v>
       </c>
@@ -67818,7 +67817,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="85" spans="1:19" hidden="1">
+    <row r="85" spans="1:19">
       <c r="A85" t="s">
         <v>110</v>
       </c>
@@ -67862,7 +67861,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1">
+    <row r="86" spans="1:19">
       <c r="A86" t="s">
         <v>110</v>
       </c>
@@ -67906,7 +67905,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="87" spans="1:19" hidden="1">
+    <row r="87" spans="1:19">
       <c r="A87" t="s">
         <v>110</v>
       </c>
@@ -67950,7 +67949,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="88" spans="1:19" hidden="1">
+    <row r="88" spans="1:19">
       <c r="A88" t="s">
         <v>110</v>
       </c>
@@ -67994,7 +67993,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="89" spans="1:19" hidden="1">
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
         <v>110</v>
       </c>
@@ -68038,7 +68037,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1">
+    <row r="90" spans="1:19">
       <c r="A90" t="s">
         <v>110</v>
       </c>
@@ -68085,7 +68084,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="91" spans="1:19" hidden="1">
+    <row r="91" spans="1:19">
       <c r="A91" t="s">
         <v>110</v>
       </c>
@@ -68132,7 +68131,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="92" spans="1:19" hidden="1">
+    <row r="92" spans="1:19">
       <c r="A92" t="s">
         <v>110</v>
       </c>
@@ -68179,7 +68178,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="93" spans="1:19" hidden="1">
+    <row r="93" spans="1:19">
       <c r="A93" t="s">
         <v>110</v>
       </c>
@@ -68223,7 +68222,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="94" spans="1:19" hidden="1">
+    <row r="94" spans="1:19">
       <c r="A94" t="s">
         <v>110</v>
       </c>
@@ -68270,7 +68269,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="95" spans="1:19" hidden="1">
+    <row r="95" spans="1:19">
       <c r="A95" t="s">
         <v>110</v>
       </c>
@@ -68317,7 +68316,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="96" spans="1:19" hidden="1">
+    <row r="96" spans="1:19">
       <c r="A96" t="s">
         <v>110</v>
       </c>
@@ -68361,7 +68360,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="97" spans="1:22" hidden="1">
+    <row r="97" spans="1:22">
       <c r="A97" t="s">
         <v>110</v>
       </c>
@@ -68405,7 +68404,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="98" spans="1:22" hidden="1">
+    <row r="98" spans="1:22">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -68449,7 +68448,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="99" spans="1:22" hidden="1">
+    <row r="99" spans="1:22">
       <c r="A99" t="s">
         <v>110</v>
       </c>
@@ -68493,7 +68492,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="100" spans="1:22" hidden="1">
+    <row r="100" spans="1:22">
       <c r="A100" t="s">
         <v>110</v>
       </c>
@@ -68543,7 +68542,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="101" spans="1:22" hidden="1">
+    <row r="101" spans="1:22">
       <c r="A101" t="s">
         <v>110</v>
       </c>
@@ -68587,7 +68586,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="102" spans="1:22" hidden="1">
+    <row r="102" spans="1:22">
       <c r="A102" t="s">
         <v>110</v>
       </c>
@@ -68637,7 +68636,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="103" spans="1:22" hidden="1">
+    <row r="103" spans="1:22">
       <c r="A103" t="s">
         <v>110</v>
       </c>
@@ -68684,7 +68683,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="104" spans="1:22" hidden="1">
+    <row r="104" spans="1:22">
       <c r="A104" t="s">
         <v>110</v>
       </c>
@@ -68728,7 +68727,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="105" spans="1:22" hidden="1">
+    <row r="105" spans="1:22">
       <c r="A105" t="s">
         <v>110</v>
       </c>
@@ -68772,7 +68771,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="106" spans="1:22" s="33" customFormat="1" hidden="1">
+    <row r="106" spans="1:22" s="33" customFormat="1">
       <c r="A106" s="33" t="s">
         <v>110</v>
       </c>
@@ -68822,7 +68821,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="107" spans="1:22" s="33" customFormat="1" hidden="1">
+    <row r="107" spans="1:22" s="33" customFormat="1">
       <c r="A107" s="33" t="s">
         <v>110</v>
       </c>
@@ -68872,7 +68871,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="108" spans="1:22" s="33" customFormat="1" hidden="1">
+    <row r="108" spans="1:22" s="33" customFormat="1">
       <c r="A108" s="33" t="s">
         <v>110</v>
       </c>
@@ -68919,7 +68918,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="109" spans="1:22" s="33" customFormat="1" hidden="1">
+    <row r="109" spans="1:22" s="33" customFormat="1">
       <c r="A109" s="33" t="s">
         <v>110</v>
       </c>
@@ -68966,7 +68965,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="110" spans="1:22" s="33" customFormat="1" hidden="1">
+    <row r="110" spans="1:22" s="33" customFormat="1">
       <c r="A110" s="33" t="s">
         <v>110</v>
       </c>
@@ -69013,7 +69012,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="111" spans="1:22" s="33" customFormat="1" hidden="1">
+    <row r="111" spans="1:22" s="33" customFormat="1">
       <c r="A111" s="33" t="s">
         <v>110</v>
       </c>
@@ -69060,7 +69059,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="112" spans="1:22" s="33" customFormat="1" hidden="1">
+    <row r="112" spans="1:22" s="33" customFormat="1">
       <c r="A112" s="33" t="s">
         <v>110</v>
       </c>
@@ -69110,7 +69109,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="113" spans="1:19" s="33" customFormat="1" hidden="1">
+    <row r="113" spans="1:19" s="33" customFormat="1">
       <c r="A113" s="33" t="s">
         <v>110</v>
       </c>
@@ -69157,7 +69156,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="114" spans="1:19" s="33" customFormat="1" hidden="1">
+    <row r="114" spans="1:19" s="33" customFormat="1">
       <c r="A114" s="33" t="s">
         <v>110</v>
       </c>
@@ -69204,7 +69203,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="115" spans="1:19" s="33" customFormat="1" hidden="1">
+    <row r="115" spans="1:19" s="33" customFormat="1">
       <c r="A115" s="33" t="s">
         <v>110</v>
       </c>
@@ -69251,7 +69250,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="116" spans="1:19" hidden="1">
+    <row r="116" spans="1:19">
       <c r="A116" t="s">
         <v>110</v>
       </c>
@@ -69301,7 +69300,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="117" spans="1:19" hidden="1">
+    <row r="117" spans="1:19">
       <c r="A117" t="s">
         <v>110</v>
       </c>
@@ -69348,7 +69347,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="118" spans="1:19" hidden="1">
+    <row r="118" spans="1:19">
       <c r="A118" t="s">
         <v>110</v>
       </c>
@@ -69398,7 +69397,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="119" spans="1:19" hidden="1">
+    <row r="119" spans="1:19">
       <c r="A119" t="s">
         <v>110</v>
       </c>
@@ -69448,7 +69447,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="120" spans="1:19" hidden="1">
+    <row r="120" spans="1:19">
       <c r="A120" t="s">
         <v>110</v>
       </c>
@@ -69498,7 +69497,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="121" spans="1:19" hidden="1">
+    <row r="121" spans="1:19">
       <c r="A121" t="s">
         <v>110</v>
       </c>
@@ -69542,7 +69541,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="122" spans="1:19" hidden="1">
+    <row r="122" spans="1:19">
       <c r="A122" t="s">
         <v>110</v>
       </c>
@@ -69589,7 +69588,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="123" spans="1:19" hidden="1">
+    <row r="123" spans="1:19">
       <c r="A123" t="s">
         <v>110</v>
       </c>
@@ -69636,7 +69635,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="124" spans="1:19" hidden="1">
+    <row r="124" spans="1:19">
       <c r="A124" t="s">
         <v>110</v>
       </c>
@@ -69683,7 +69682,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="125" spans="1:19" hidden="1">
+    <row r="125" spans="1:19">
       <c r="A125" t="s">
         <v>110</v>
       </c>
@@ -69730,7 +69729,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="126" spans="1:19" hidden="1">
+    <row r="126" spans="1:19">
       <c r="A126" t="s">
         <v>110</v>
       </c>
@@ -69780,7 +69779,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="127" spans="1:19" hidden="1">
+    <row r="127" spans="1:19">
       <c r="A127" t="s">
         <v>110</v>
       </c>
@@ -69830,7 +69829,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="128" spans="1:19" hidden="1">
+    <row r="128" spans="1:19">
       <c r="A128" t="s">
         <v>110</v>
       </c>
@@ -69880,7 +69879,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="129" spans="1:20" hidden="1">
+    <row r="129" spans="1:20">
       <c r="A129" t="s">
         <v>110</v>
       </c>
@@ -69927,7 +69926,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="130" spans="1:20" hidden="1">
+    <row r="130" spans="1:20">
       <c r="A130" t="s">
         <v>110</v>
       </c>
@@ -69977,7 +69976,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="131" spans="1:20" hidden="1">
+    <row r="131" spans="1:20">
       <c r="A131" t="s">
         <v>110</v>
       </c>
@@ -70027,7 +70026,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="132" spans="1:20" hidden="1">
+    <row r="132" spans="1:20">
       <c r="A132" t="s">
         <v>110</v>
       </c>
@@ -70077,7 +70076,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="133" spans="1:20" hidden="1">
+    <row r="133" spans="1:20">
       <c r="A133" t="s">
         <v>110</v>
       </c>
@@ -70127,7 +70126,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="134" spans="1:20" hidden="1">
+    <row r="134" spans="1:20">
       <c r="A134" t="s">
         <v>110</v>
       </c>
@@ -70177,7 +70176,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="135" spans="1:20" hidden="1">
+    <row r="135" spans="1:20">
       <c r="A135" t="s">
         <v>110</v>
       </c>
@@ -70224,7 +70223,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="136" spans="1:20" hidden="1">
+    <row r="136" spans="1:20">
       <c r="A136" t="s">
         <v>110</v>
       </c>
@@ -70274,7 +70273,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="137" spans="1:20" hidden="1">
+    <row r="137" spans="1:20">
       <c r="A137" t="s">
         <v>110</v>
       </c>
@@ -70327,7 +70326,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="138" spans="1:20" hidden="1">
+    <row r="138" spans="1:20">
       <c r="A138" t="s">
         <v>110</v>
       </c>
@@ -70380,7 +70379,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="139" spans="1:20" hidden="1">
+    <row r="139" spans="1:20">
       <c r="A139" t="s">
         <v>4</v>
       </c>
@@ -70433,7 +70432,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="140" spans="1:20" hidden="1">
+    <row r="140" spans="1:20">
       <c r="A140" t="s">
         <v>4</v>
       </c>
@@ -70486,7 +70485,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="141" spans="1:20" hidden="1">
+    <row r="141" spans="1:20">
       <c r="A141" t="s">
         <v>4</v>
       </c>
@@ -70792,7 +70791,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="147" spans="1:20" hidden="1">
+    <row r="147" spans="1:20">
       <c r="A147" t="s">
         <v>4</v>
       </c>
@@ -70827,7 +70826,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="148" spans="1:20" hidden="1">
+    <row r="148" spans="1:20">
       <c r="A148" t="s">
         <v>4</v>
       </c>
@@ -70883,7 +70882,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="149" spans="1:20" hidden="1">
+    <row r="149" spans="1:20">
       <c r="A149" t="s">
         <v>4</v>
       </c>
@@ -70933,7 +70932,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="150" spans="1:20" hidden="1">
+    <row r="150" spans="1:20">
       <c r="A150" t="s">
         <v>4</v>
       </c>
@@ -70989,7 +70988,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="151" spans="1:20" hidden="1">
+    <row r="151" spans="1:20">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -71042,7 +71041,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="152" spans="1:20" hidden="1">
+    <row r="152" spans="1:20">
       <c r="A152" t="s">
         <v>4</v>
       </c>
@@ -71095,7 +71094,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="153" spans="1:20" hidden="1">
+    <row r="153" spans="1:20">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -71148,7 +71147,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="154" spans="1:20" hidden="1">
+    <row r="154" spans="1:20">
       <c r="A154" t="s">
         <v>4</v>
       </c>
@@ -71201,7 +71200,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="155" spans="1:20" hidden="1">
+    <row r="155" spans="1:20">
       <c r="A155" t="s">
         <v>4</v>
       </c>
@@ -71254,7 +71253,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="156" spans="1:20" hidden="1">
+    <row r="156" spans="1:20">
       <c r="A156" t="s">
         <v>4</v>
       </c>
@@ -71310,7 +71309,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="157" spans="1:20" hidden="1">
+    <row r="157" spans="1:20">
       <c r="A157" t="s">
         <v>4</v>
       </c>
@@ -71363,7 +71362,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="158" spans="1:20" hidden="1">
+    <row r="158" spans="1:20">
       <c r="A158" t="s">
         <v>4</v>
       </c>
@@ -71416,7 +71415,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="159" spans="1:20" hidden="1">
+    <row r="159" spans="1:20">
       <c r="A159" t="s">
         <v>4</v>
       </c>
@@ -71469,7 +71468,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="160" spans="1:20" hidden="1">
+    <row r="160" spans="1:20">
       <c r="A160" t="s">
         <v>4</v>
       </c>
@@ -71519,7 +71518,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="161" spans="1:20" hidden="1">
+    <row r="161" spans="1:20">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -71569,7 +71568,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="162" spans="1:20" hidden="1">
+    <row r="162" spans="1:20">
       <c r="A162" t="s">
         <v>4</v>
       </c>
@@ -71619,7 +71618,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="163" spans="1:20" hidden="1">
+    <row r="163" spans="1:20">
       <c r="A163" t="s">
         <v>4</v>
       </c>
@@ -71669,7 +71668,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="164" spans="1:20" hidden="1">
+    <row r="164" spans="1:20">
       <c r="A164" t="s">
         <v>4</v>
       </c>
@@ -71719,7 +71718,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="165" spans="1:20" hidden="1">
+    <row r="165" spans="1:20">
       <c r="A165" t="s">
         <v>4</v>
       </c>
@@ -72257,7 +72256,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="176" spans="1:20" hidden="1">
+    <row r="176" spans="1:20">
       <c r="A176" t="s">
         <v>4</v>
       </c>
@@ -72313,7 +72312,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="177" spans="1:20" hidden="1">
+    <row r="177" spans="1:20">
       <c r="A177" t="s">
         <v>4</v>
       </c>
@@ -72366,7 +72365,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="178" spans="1:20" hidden="1">
+    <row r="178" spans="1:20">
       <c r="A178" t="s">
         <v>4</v>
       </c>
@@ -72578,7 +72577,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="182" spans="1:20" hidden="1">
+    <row r="182" spans="1:20">
       <c r="A182" t="s">
         <v>4</v>
       </c>
@@ -72631,7 +72630,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="183" spans="1:20" hidden="1">
+    <row r="183" spans="1:20">
       <c r="A183" t="s">
         <v>4</v>
       </c>
@@ -72678,7 +72677,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="184" spans="1:20" hidden="1">
+    <row r="184" spans="1:20">
       <c r="A184" t="s">
         <v>4</v>
       </c>
@@ -72728,7 +72727,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="185" spans="1:20" hidden="1">
+    <row r="185" spans="1:20">
       <c r="A185" t="s">
         <v>4</v>
       </c>
@@ -72778,7 +72777,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="186" spans="1:20" hidden="1">
+    <row r="186" spans="1:20">
       <c r="A186" t="s">
         <v>4</v>
       </c>
@@ -72828,7 +72827,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="187" spans="1:20" hidden="1">
+    <row r="187" spans="1:20">
       <c r="A187" t="s">
         <v>4</v>
       </c>
@@ -72878,7 +72877,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="188" spans="1:20" hidden="1">
+    <row r="188" spans="1:20">
       <c r="A188" t="s">
         <v>4</v>
       </c>
@@ -72925,7 +72924,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="189" spans="1:20" hidden="1">
+    <row r="189" spans="1:20">
       <c r="A189" t="s">
         <v>4</v>
       </c>
@@ -72975,7 +72974,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="190" spans="1:20" hidden="1">
+    <row r="190" spans="1:20">
       <c r="A190" t="s">
         <v>4</v>
       </c>
@@ -73031,7 +73030,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="191" spans="1:20" hidden="1">
+    <row r="191" spans="1:20">
       <c r="A191" t="s">
         <v>4</v>
       </c>
@@ -73081,7 +73080,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="192" spans="1:20" hidden="1">
+    <row r="192" spans="1:20">
       <c r="A192" t="s">
         <v>4</v>
       </c>
@@ -73128,7 +73127,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="193" spans="1:20" hidden="1">
+    <row r="193" spans="1:20">
       <c r="A193" t="s">
         <v>4</v>
       </c>
@@ -73175,7 +73174,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="194" spans="1:20" hidden="1">
+    <row r="194" spans="1:20">
       <c r="A194" t="s">
         <v>4</v>
       </c>
@@ -73225,7 +73224,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="195" spans="1:20" hidden="1">
+    <row r="195" spans="1:20">
       <c r="A195" t="s">
         <v>4</v>
       </c>
@@ -73275,7 +73274,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="196" spans="1:20" hidden="1">
+    <row r="196" spans="1:20">
       <c r="A196" t="s">
         <v>4</v>
       </c>
@@ -73325,7 +73324,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="197" spans="1:20" hidden="1">
+    <row r="197" spans="1:20">
       <c r="A197" t="s">
         <v>4</v>
       </c>
@@ -73372,7 +73371,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="198" spans="1:20" hidden="1">
+    <row r="198" spans="1:20">
       <c r="A198" t="s">
         <v>4</v>
       </c>
@@ -73419,7 +73418,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="199" spans="1:20" hidden="1">
+    <row r="199" spans="1:20">
       <c r="A199" t="s">
         <v>4</v>
       </c>
@@ -73466,7 +73465,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="200" spans="1:20" hidden="1">
+    <row r="200" spans="1:20">
       <c r="A200" t="s">
         <v>4</v>
       </c>
@@ -73513,7 +73512,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="201" spans="1:20" hidden="1">
+    <row r="201" spans="1:20">
       <c r="A201" t="s">
         <v>4</v>
       </c>
@@ -73563,7 +73562,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="202" spans="1:20" hidden="1">
+    <row r="202" spans="1:20">
       <c r="A202" t="s">
         <v>4</v>
       </c>
@@ -73616,7 +73615,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="203" spans="1:20" hidden="1">
+    <row r="203" spans="1:20">
       <c r="A203" t="s">
         <v>4</v>
       </c>
@@ -73666,7 +73665,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="204" spans="1:20" hidden="1">
+    <row r="204" spans="1:20">
       <c r="A204" t="s">
         <v>4</v>
       </c>
@@ -73719,7 +73718,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="205" spans="1:20" hidden="1">
+    <row r="205" spans="1:20">
       <c r="A205" t="s">
         <v>4</v>
       </c>
@@ -73769,7 +73768,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="206" spans="1:20" hidden="1">
+    <row r="206" spans="1:20">
       <c r="A206" t="s">
         <v>4</v>
       </c>
@@ -73828,7 +73827,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="207" spans="1:20" hidden="1">
+    <row r="207" spans="1:20">
       <c r="A207" t="s">
         <v>4</v>
       </c>
@@ -73937,7 +73936,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="209" spans="1:20" hidden="1">
+    <row r="209" spans="1:20">
       <c r="A209" t="s">
         <v>4</v>
       </c>
@@ -74320,7 +74319,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="216" spans="1:20" hidden="1">
+    <row r="216" spans="1:20">
       <c r="A216" t="s">
         <v>4</v>
       </c>
@@ -74376,7 +74375,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="217" spans="1:20" hidden="1">
+    <row r="217" spans="1:20">
       <c r="A217" t="s">
         <v>4</v>
       </c>
@@ -74867,7 +74866,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="227" spans="1:20" hidden="1">
+    <row r="227" spans="1:20">
       <c r="A227" t="s">
         <v>4</v>
       </c>
@@ -74905,7 +74904,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="228" spans="1:20" hidden="1">
+    <row r="228" spans="1:20">
       <c r="A228" t="s">
         <v>4</v>
       </c>
@@ -74946,7 +74945,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="229" spans="1:20" hidden="1">
+    <row r="229" spans="1:20">
       <c r="A229" t="s">
         <v>4</v>
       </c>
@@ -74984,7 +74983,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:20" hidden="1">
+    <row r="230" spans="1:20">
       <c r="A230" t="s">
         <v>4</v>
       </c>
@@ -75022,7 +75021,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="231" spans="1:20" hidden="1">
+    <row r="231" spans="1:20">
       <c r="A231" t="s">
         <v>4</v>
       </c>
@@ -75281,7 +75280,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="236" spans="1:20" hidden="1">
+    <row r="236" spans="1:20">
       <c r="A236" t="s">
         <v>4</v>
       </c>
@@ -75331,7 +75330,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="237" spans="1:20" hidden="1">
+    <row r="237" spans="1:20">
       <c r="A237" t="s">
         <v>69</v>
       </c>
@@ -75381,7 +75380,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="238" spans="1:20" hidden="1">
+    <row r="238" spans="1:20">
       <c r="A238" t="s">
         <v>69</v>
       </c>
@@ -75434,7 +75433,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="239" spans="1:20" hidden="1">
+    <row r="239" spans="1:20">
       <c r="A239" t="s">
         <v>69</v>
       </c>
@@ -75484,7 +75483,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="240" spans="1:20" hidden="1">
+    <row r="240" spans="1:20">
       <c r="A240" t="s">
         <v>69</v>
       </c>
@@ -75534,7 +75533,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="241" spans="1:20" hidden="1">
+    <row r="241" spans="1:20">
       <c r="A241" t="s">
         <v>69</v>
       </c>
@@ -75584,7 +75583,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="242" spans="1:20" hidden="1">
+    <row r="242" spans="1:20">
       <c r="A242" t="s">
         <v>69</v>
       </c>
@@ -75628,7 +75627,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="243" spans="1:20" hidden="1">
+    <row r="243" spans="1:20">
       <c r="A243" t="s">
         <v>69</v>
       </c>
@@ -75678,7 +75677,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="244" spans="1:20" hidden="1">
+    <row r="244" spans="1:20">
       <c r="A244" t="s">
         <v>69</v>
       </c>
@@ -75728,7 +75727,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="245" spans="1:20" hidden="1">
+    <row r="245" spans="1:20">
       <c r="A245" t="s">
         <v>69</v>
       </c>
@@ -75781,7 +75780,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="246" spans="1:20" hidden="1">
+    <row r="246" spans="1:20">
       <c r="A246" t="s">
         <v>69</v>
       </c>
@@ -75831,7 +75830,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="247" spans="1:20" hidden="1">
+    <row r="247" spans="1:20">
       <c r="A247" t="s">
         <v>69</v>
       </c>
@@ -75878,7 +75877,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="248" spans="1:20" hidden="1">
+    <row r="248" spans="1:20">
       <c r="A248" t="s">
         <v>69</v>
       </c>
@@ -75925,7 +75924,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="249" spans="1:20" hidden="1">
+    <row r="249" spans="1:20">
       <c r="A249" t="s">
         <v>69</v>
       </c>
@@ -75975,7 +75974,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="250" spans="1:20" hidden="1">
+    <row r="250" spans="1:20">
       <c r="A250" t="s">
         <v>69</v>
       </c>
@@ -76025,7 +76024,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="251" spans="1:20" hidden="1">
+    <row r="251" spans="1:20">
       <c r="A251" t="s">
         <v>69</v>
       </c>
@@ -76072,7 +76071,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="252" spans="1:20" hidden="1">
+    <row r="252" spans="1:20">
       <c r="A252" t="s">
         <v>69</v>
       </c>
@@ -76122,7 +76121,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="253" spans="1:20" hidden="1">
+    <row r="253" spans="1:20">
       <c r="A253" t="s">
         <v>69</v>
       </c>
@@ -76175,7 +76174,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="254" spans="1:20" hidden="1">
+    <row r="254" spans="1:20">
       <c r="A254" t="s">
         <v>69</v>
       </c>
@@ -76225,7 +76224,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="255" spans="1:20" hidden="1">
+    <row r="255" spans="1:20">
       <c r="A255" t="s">
         <v>69</v>
       </c>
@@ -76278,7 +76277,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="256" spans="1:20" hidden="1">
+    <row r="256" spans="1:20">
       <c r="A256" t="s">
         <v>69</v>
       </c>
@@ -76331,7 +76330,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="257" spans="1:20" hidden="1">
+    <row r="257" spans="1:20">
       <c r="A257" t="s">
         <v>69</v>
       </c>
@@ -76384,7 +76383,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="258" spans="1:20" hidden="1">
+    <row r="258" spans="1:20">
       <c r="A258" t="s">
         <v>69</v>
       </c>
@@ -76434,7 +76433,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="259" spans="1:20" hidden="1">
+    <row r="259" spans="1:20">
       <c r="A259" t="s">
         <v>69</v>
       </c>
@@ -76484,7 +76483,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="260" spans="1:20" hidden="1">
+    <row r="260" spans="1:20">
       <c r="A260" t="s">
         <v>69</v>
       </c>
@@ -76534,7 +76533,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="261" spans="1:20" hidden="1">
+    <row r="261" spans="1:20">
       <c r="A261" t="s">
         <v>69</v>
       </c>
@@ -76584,7 +76583,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="262" spans="1:20" hidden="1">
+    <row r="262" spans="1:20">
       <c r="A262" t="s">
         <v>69</v>
       </c>
@@ -76631,7 +76630,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="263" spans="1:20" hidden="1">
+    <row r="263" spans="1:20">
       <c r="A263" t="s">
         <v>69</v>
       </c>
@@ -76678,7 +76677,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="264" spans="1:20" hidden="1">
+    <row r="264" spans="1:20">
       <c r="A264" t="s">
         <v>69</v>
       </c>
@@ -76725,7 +76724,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="265" spans="1:20" hidden="1">
+    <row r="265" spans="1:20">
       <c r="A265" t="s">
         <v>69</v>
       </c>
@@ -76772,7 +76771,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="266" spans="1:20" hidden="1">
+    <row r="266" spans="1:20">
       <c r="A266" t="s">
         <v>69</v>
       </c>
@@ -76819,7 +76818,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="267" spans="1:20" hidden="1">
+    <row r="267" spans="1:20">
       <c r="A267" t="s">
         <v>69</v>
       </c>
@@ -76869,7 +76868,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="268" spans="1:20" hidden="1">
+    <row r="268" spans="1:20">
       <c r="A268" t="s">
         <v>69</v>
       </c>
@@ -76916,7 +76915,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="269" spans="1:20" hidden="1">
+    <row r="269" spans="1:20">
       <c r="A269" t="s">
         <v>69</v>
       </c>
@@ -76969,7 +76968,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="270" spans="1:20" hidden="1">
+    <row r="270" spans="1:20">
       <c r="A270" t="s">
         <v>69</v>
       </c>
@@ -77016,7 +77015,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="271" spans="1:20" hidden="1">
+    <row r="271" spans="1:20">
       <c r="A271" t="s">
         <v>69</v>
       </c>
@@ -77069,7 +77068,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="272" spans="1:20" hidden="1">
+    <row r="272" spans="1:20">
       <c r="A272" t="s">
         <v>69</v>
       </c>
@@ -77119,7 +77118,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="273" spans="1:20" hidden="1">
+    <row r="273" spans="1:20">
       <c r="A273" t="s">
         <v>69</v>
       </c>
@@ -77169,7 +77168,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="274" spans="1:20" hidden="1">
+    <row r="274" spans="1:20">
       <c r="A274" t="s">
         <v>164</v>
       </c>
@@ -77222,7 +77221,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="275" spans="1:20" hidden="1">
+    <row r="275" spans="1:20">
       <c r="A275" t="s">
         <v>164</v>
       </c>
@@ -77272,7 +77271,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="276" spans="1:20" hidden="1">
+    <row r="276" spans="1:20">
       <c r="A276" t="s">
         <v>164</v>
       </c>
@@ -77322,7 +77321,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="277" spans="1:20" hidden="1">
+    <row r="277" spans="1:20">
       <c r="A277" t="s">
         <v>164</v>
       </c>
@@ -77372,7 +77371,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="278" spans="1:20" hidden="1">
+    <row r="278" spans="1:20">
       <c r="A278" t="s">
         <v>164</v>
       </c>
@@ -77422,7 +77421,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="279" spans="1:20" hidden="1">
+    <row r="279" spans="1:20">
       <c r="A279" t="s">
         <v>164</v>
       </c>
@@ -77472,7 +77471,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="280" spans="1:20" hidden="1">
+    <row r="280" spans="1:20">
       <c r="A280" t="s">
         <v>164</v>
       </c>
@@ -77525,7 +77524,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="281" spans="1:20" hidden="1">
+    <row r="281" spans="1:20">
       <c r="A281" t="s">
         <v>164</v>
       </c>
@@ -77572,7 +77571,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="282" spans="1:20" hidden="1">
+    <row r="282" spans="1:20">
       <c r="A282" t="s">
         <v>164</v>
       </c>
@@ -77622,7 +77621,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="283" spans="1:20" hidden="1">
+    <row r="283" spans="1:20">
       <c r="A283" t="s">
         <v>164</v>
       </c>
@@ -77672,7 +77671,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="284" spans="1:20" hidden="1">
+    <row r="284" spans="1:20">
       <c r="A284" t="s">
         <v>164</v>
       </c>
@@ -77722,7 +77721,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="285" spans="1:20" hidden="1">
+    <row r="285" spans="1:20">
       <c r="A285" t="s">
         <v>164</v>
       </c>
@@ -77772,7 +77771,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="286" spans="1:20" hidden="1">
+    <row r="286" spans="1:20">
       <c r="A286" t="s">
         <v>164</v>
       </c>
@@ -77822,7 +77821,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="287" spans="1:20" hidden="1">
+    <row r="287" spans="1:20">
       <c r="A287" t="s">
         <v>164</v>
       </c>
@@ -77875,7 +77874,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="288" spans="1:20" hidden="1">
+    <row r="288" spans="1:20">
       <c r="A288" t="s">
         <v>164</v>
       </c>
@@ -77928,7 +77927,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="289" spans="1:20" hidden="1">
+    <row r="289" spans="1:20">
       <c r="A289" t="s">
         <v>164</v>
       </c>
@@ -77981,7 +77980,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="290" spans="1:20" hidden="1">
+    <row r="290" spans="1:20">
       <c r="A290" t="s">
         <v>164</v>
       </c>
@@ -78034,7 +78033,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="291" spans="1:20" hidden="1">
+    <row r="291" spans="1:20">
       <c r="A291" t="s">
         <v>164</v>
       </c>
@@ -78087,7 +78086,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="292" spans="1:20" hidden="1">
+    <row r="292" spans="1:20">
       <c r="A292" t="s">
         <v>164</v>
       </c>
@@ -78140,7 +78139,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="293" spans="1:20" hidden="1">
+    <row r="293" spans="1:20">
       <c r="A293" t="s">
         <v>164</v>
       </c>
@@ -78190,7 +78189,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="294" spans="1:20" hidden="1">
+    <row r="294" spans="1:20">
       <c r="A294" t="s">
         <v>164</v>
       </c>
@@ -78240,7 +78239,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="295" spans="1:20" hidden="1">
+    <row r="295" spans="1:20">
       <c r="A295" t="s">
         <v>164</v>
       </c>
@@ -78290,7 +78289,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="296" spans="1:20" hidden="1">
+    <row r="296" spans="1:20">
       <c r="A296" t="s">
         <v>164</v>
       </c>
@@ -78343,7 +78342,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="297" spans="1:20" hidden="1">
+    <row r="297" spans="1:20">
       <c r="A297" t="s">
         <v>164</v>
       </c>
@@ -78393,7 +78392,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="298" spans="1:20" hidden="1">
+    <row r="298" spans="1:20">
       <c r="A298" t="s">
         <v>164</v>
       </c>
@@ -78443,7 +78442,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="299" spans="1:20" hidden="1">
+    <row r="299" spans="1:20">
       <c r="A299" t="s">
         <v>164</v>
       </c>
@@ -78493,7 +78492,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="300" spans="1:20" hidden="1">
+    <row r="300" spans="1:20">
       <c r="A300" t="s">
         <v>164</v>
       </c>
@@ -78546,7 +78545,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="301" spans="1:20" hidden="1">
+    <row r="301" spans="1:20">
       <c r="A301" t="s">
         <v>164</v>
       </c>
@@ -78596,7 +78595,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="302" spans="1:20" hidden="1">
+    <row r="302" spans="1:20">
       <c r="A302" t="s">
         <v>164</v>
       </c>
@@ -78649,7 +78648,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="303" spans="1:20" hidden="1">
+    <row r="303" spans="1:20">
       <c r="A303" t="s">
         <v>164</v>
       </c>
@@ -78699,7 +78698,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="304" spans="1:20" hidden="1">
+    <row r="304" spans="1:20">
       <c r="A304" t="s">
         <v>164</v>
       </c>
@@ -78749,7 +78748,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="305" spans="1:20" hidden="1">
+    <row r="305" spans="1:20">
       <c r="A305" t="s">
         <v>164</v>
       </c>
@@ -78796,7 +78795,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="306" spans="1:20" hidden="1">
+    <row r="306" spans="1:20">
       <c r="A306" t="s">
         <v>164</v>
       </c>
@@ -78849,7 +78848,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="307" spans="1:20" hidden="1">
+    <row r="307" spans="1:20">
       <c r="A307" t="s">
         <v>164</v>
       </c>
@@ -78902,7 +78901,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="308" spans="1:20" hidden="1">
+    <row r="308" spans="1:20">
       <c r="A308" t="s">
         <v>164</v>
       </c>
@@ -78955,7 +78954,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="309" spans="1:20" hidden="1">
+    <row r="309" spans="1:20">
       <c r="A309" t="s">
         <v>164</v>
       </c>
@@ -79005,7 +79004,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="310" spans="1:20" hidden="1">
+    <row r="310" spans="1:20">
       <c r="A310" t="s">
         <v>164</v>
       </c>
@@ -79055,7 +79054,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="311" spans="1:20" hidden="1">
+    <row r="311" spans="1:20">
       <c r="A311" t="s">
         <v>164</v>
       </c>
@@ -79105,7 +79104,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="312" spans="1:20" hidden="1">
+    <row r="312" spans="1:20">
       <c r="A312" t="s">
         <v>164</v>
       </c>
@@ -79158,7 +79157,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="313" spans="1:20" hidden="1">
+    <row r="313" spans="1:20">
       <c r="A313" t="s">
         <v>164</v>
       </c>
@@ -79208,7 +79207,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="314" spans="1:20" hidden="1">
+    <row r="314" spans="1:20">
       <c r="A314" t="s">
         <v>164</v>
       </c>
@@ -79258,7 +79257,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="315" spans="1:20" hidden="1">
+    <row r="315" spans="1:20">
       <c r="A315" t="s">
         <v>164</v>
       </c>
@@ -79308,7 +79307,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="316" spans="1:20" hidden="1">
+    <row r="316" spans="1:20">
       <c r="A316" t="s">
         <v>164</v>
       </c>
@@ -79364,7 +79363,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="317" spans="1:20" hidden="1">
+    <row r="317" spans="1:20">
       <c r="A317" t="s">
         <v>164</v>
       </c>
@@ -79420,7 +79419,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="318" spans="1:20" hidden="1">
+    <row r="318" spans="1:20">
       <c r="A318" t="s">
         <v>164</v>
       </c>
@@ -79476,7 +79475,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="319" spans="1:20" hidden="1">
+    <row r="319" spans="1:20">
       <c r="A319" t="s">
         <v>164</v>
       </c>
@@ -79526,7 +79525,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="320" spans="1:20" hidden="1">
+    <row r="320" spans="1:20">
       <c r="A320" t="s">
         <v>164</v>
       </c>
@@ -79576,7 +79575,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="321" spans="1:20" hidden="1">
+    <row r="321" spans="1:20">
       <c r="A321" t="s">
         <v>164</v>
       </c>
@@ -79626,7 +79625,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="322" spans="1:20" hidden="1">
+    <row r="322" spans="1:20">
       <c r="A322" t="s">
         <v>164</v>
       </c>
@@ -79676,7 +79675,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="323" spans="1:20" hidden="1">
+    <row r="323" spans="1:20">
       <c r="A323" t="s">
         <v>164</v>
       </c>
@@ -79729,7 +79728,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="324" spans="1:20" hidden="1">
+    <row r="324" spans="1:20">
       <c r="A324" t="s">
         <v>164</v>
       </c>
@@ -79776,7 +79775,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="325" spans="1:20" hidden="1">
+    <row r="325" spans="1:20">
       <c r="A325" t="s">
         <v>164</v>
       </c>
@@ -79829,7 +79828,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="326" spans="1:20" hidden="1">
+    <row r="326" spans="1:20">
       <c r="A326" t="s">
         <v>164</v>
       </c>
@@ -79882,7 +79881,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="327" spans="1:20" hidden="1">
+    <row r="327" spans="1:20">
       <c r="A327" t="s">
         <v>164</v>
       </c>
@@ -79935,7 +79934,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="328" spans="1:20" hidden="1">
+    <row r="328" spans="1:20">
       <c r="A328" t="s">
         <v>164</v>
       </c>
@@ -79991,7 +79990,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="329" spans="1:20" hidden="1">
+    <row r="329" spans="1:20">
       <c r="A329" t="s">
         <v>102</v>
       </c>
@@ -80041,7 +80040,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="330" spans="1:20" hidden="1">
+    <row r="330" spans="1:20">
       <c r="A330" t="s">
         <v>102</v>
       </c>
@@ -80094,7 +80093,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="331" spans="1:20" hidden="1">
+    <row r="331" spans="1:20">
       <c r="A331" t="s">
         <v>102</v>
       </c>
@@ -80150,7 +80149,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="332" spans="1:20" hidden="1">
+    <row r="332" spans="1:20">
       <c r="A332" t="s">
         <v>102</v>
       </c>
@@ -80197,7 +80196,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="333" spans="1:20" hidden="1">
+    <row r="333" spans="1:20">
       <c r="A333" t="s">
         <v>102</v>
       </c>
@@ -80247,7 +80246,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="334" spans="1:20" hidden="1">
+    <row r="334" spans="1:20">
       <c r="A334" t="s">
         <v>102</v>
       </c>
@@ -80297,7 +80296,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="335" spans="1:20" hidden="1">
+    <row r="335" spans="1:20">
       <c r="A335" t="s">
         <v>102</v>
       </c>
@@ -80350,7 +80349,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="336" spans="1:20" hidden="1">
+    <row r="336" spans="1:20">
       <c r="A336" t="s">
         <v>102</v>
       </c>
@@ -80403,7 +80402,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="337" spans="1:20" hidden="1">
+    <row r="337" spans="1:20">
       <c r="A337" t="s">
         <v>102</v>
       </c>
@@ -80456,7 +80455,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="338" spans="1:20" hidden="1">
+    <row r="338" spans="1:20">
       <c r="A338" t="s">
         <v>102</v>
       </c>
@@ -80509,7 +80508,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="339" spans="1:20" hidden="1">
+    <row r="339" spans="1:20">
       <c r="A339" t="s">
         <v>102</v>
       </c>
@@ -80562,7 +80561,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="340" spans="1:20" hidden="1">
+    <row r="340" spans="1:20">
       <c r="A340" t="s">
         <v>102</v>
       </c>
@@ -80618,7 +80617,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="341" spans="1:20" hidden="1">
+    <row r="341" spans="1:20">
       <c r="A341" t="s">
         <v>102</v>
       </c>
@@ -80674,7 +80673,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="342" spans="1:20" hidden="1">
+    <row r="342" spans="1:20">
       <c r="A342" t="s">
         <v>102</v>
       </c>
@@ -80727,7 +80726,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="343" spans="1:20" hidden="1">
+    <row r="343" spans="1:20">
       <c r="A343" t="s">
         <v>102</v>
       </c>
@@ -80777,7 +80776,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="344" spans="1:20" hidden="1">
+    <row r="344" spans="1:20">
       <c r="A344" t="s">
         <v>205</v>
       </c>
@@ -80821,7 +80820,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="345" spans="1:20" hidden="1">
+    <row r="345" spans="1:20">
       <c r="A345" t="s">
         <v>205</v>
       </c>
@@ -80871,7 +80870,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="346" spans="1:20" hidden="1">
+    <row r="346" spans="1:20">
       <c r="A346" t="s">
         <v>205</v>
       </c>
@@ -80918,7 +80917,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="347" spans="1:20" hidden="1">
+    <row r="347" spans="1:20">
       <c r="A347" t="s">
         <v>205</v>
       </c>
@@ -80965,7 +80964,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="348" spans="1:20" hidden="1">
+    <row r="348" spans="1:20">
       <c r="A348" t="s">
         <v>205</v>
       </c>
@@ -81012,7 +81011,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="349" spans="1:20" hidden="1">
+    <row r="349" spans="1:20">
       <c r="A349" t="s">
         <v>205</v>
       </c>
@@ -81059,7 +81058,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="350" spans="1:20" hidden="1">
+    <row r="350" spans="1:20">
       <c r="A350" t="s">
         <v>205</v>
       </c>
@@ -81106,7 +81105,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="351" spans="1:20" hidden="1">
+    <row r="351" spans="1:20">
       <c r="A351" t="s">
         <v>205</v>
       </c>
@@ -81153,7 +81152,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="352" spans="1:20" hidden="1">
+    <row r="352" spans="1:20">
       <c r="A352" t="s">
         <v>205</v>
       </c>
@@ -81200,7 +81199,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="353" spans="1:18" hidden="1">
+    <row r="353" spans="1:18">
       <c r="A353" t="s">
         <v>205</v>
       </c>
@@ -81247,7 +81246,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="354" spans="1:18" hidden="1">
+    <row r="354" spans="1:18">
       <c r="A354" t="s">
         <v>205</v>
       </c>
@@ -81294,7 +81293,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="355" spans="1:18" hidden="1">
+    <row r="355" spans="1:18">
       <c r="A355" t="s">
         <v>205</v>
       </c>
@@ -81341,7 +81340,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="356" spans="1:18" hidden="1">
+    <row r="356" spans="1:18">
       <c r="A356" t="s">
         <v>205</v>
       </c>
@@ -81388,7 +81387,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="357" spans="1:18" hidden="1">
+    <row r="357" spans="1:18">
       <c r="A357" t="s">
         <v>205</v>
       </c>
@@ -81435,7 +81434,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="358" spans="1:18" hidden="1">
+    <row r="358" spans="1:18">
       <c r="A358" t="s">
         <v>205</v>
       </c>
@@ -81482,7 +81481,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="359" spans="1:18" hidden="1">
+    <row r="359" spans="1:18">
       <c r="A359" t="s">
         <v>205</v>
       </c>
@@ -81529,7 +81528,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="360" spans="1:18" hidden="1">
+    <row r="360" spans="1:18">
       <c r="A360" t="s">
         <v>205</v>
       </c>
@@ -81576,7 +81575,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="361" spans="1:18" hidden="1">
+    <row r="361" spans="1:18">
       <c r="A361" t="s">
         <v>205</v>
       </c>
@@ -81623,7 +81622,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="362" spans="1:18" hidden="1">
+    <row r="362" spans="1:18">
       <c r="A362" t="s">
         <v>205</v>
       </c>
@@ -81670,7 +81669,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="363" spans="1:18" hidden="1">
+    <row r="363" spans="1:18">
       <c r="A363" t="s">
         <v>205</v>
       </c>
@@ -81717,7 +81716,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="364" spans="1:18" hidden="1">
+    <row r="364" spans="1:18">
       <c r="A364" t="s">
         <v>205</v>
       </c>
@@ -81764,7 +81763,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="365" spans="1:18" hidden="1">
+    <row r="365" spans="1:18">
       <c r="A365" t="s">
         <v>205</v>
       </c>
@@ -81808,7 +81807,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="366" spans="1:18" hidden="1">
+    <row r="366" spans="1:18">
       <c r="A366" t="s">
         <v>205</v>
       </c>
@@ -81852,7 +81851,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="367" spans="1:18" hidden="1">
+    <row r="367" spans="1:18">
       <c r="A367" t="s">
         <v>205</v>
       </c>
@@ -81896,7 +81895,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="368" spans="1:18" hidden="1">
+    <row r="368" spans="1:18">
       <c r="A368" t="s">
         <v>205</v>
       </c>
@@ -81943,7 +81942,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="369" spans="1:18" hidden="1">
+    <row r="369" spans="1:18">
       <c r="A369" t="s">
         <v>205</v>
       </c>
@@ -81990,7 +81989,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="370" spans="1:18" hidden="1">
+    <row r="370" spans="1:18">
       <c r="A370" t="s">
         <v>205</v>
       </c>
@@ -82037,7 +82036,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="371" spans="1:18" hidden="1">
+    <row r="371" spans="1:18">
       <c r="A371" t="s">
         <v>205</v>
       </c>
@@ -82084,7 +82083,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="372" spans="1:18" hidden="1">
+    <row r="372" spans="1:18">
       <c r="A372" t="s">
         <v>205</v>
       </c>
@@ -82131,7 +82130,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="373" spans="1:18" hidden="1">
+    <row r="373" spans="1:18">
       <c r="A373" t="s">
         <v>205</v>
       </c>
@@ -82178,7 +82177,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="374" spans="1:18" hidden="1">
+    <row r="374" spans="1:18">
       <c r="A374" t="s">
         <v>205</v>
       </c>
@@ -82225,7 +82224,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="375" spans="1:18" hidden="1">
+    <row r="375" spans="1:18">
       <c r="A375" t="s">
         <v>205</v>
       </c>
@@ -82272,7 +82271,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="376" spans="1:18" hidden="1">
+    <row r="376" spans="1:18">
       <c r="A376" t="s">
         <v>205</v>
       </c>
@@ -82322,7 +82321,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="377" spans="1:18" hidden="1">
+    <row r="377" spans="1:18">
       <c r="A377" t="s">
         <v>205</v>
       </c>
@@ -82369,7 +82368,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="378" spans="1:18" hidden="1">
+    <row r="378" spans="1:18">
       <c r="A378" t="s">
         <v>205</v>
       </c>
@@ -82416,7 +82415,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="379" spans="1:18" hidden="1">
+    <row r="379" spans="1:18">
       <c r="A379" t="s">
         <v>205</v>
       </c>
@@ -82463,7 +82462,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="380" spans="1:18" hidden="1">
+    <row r="380" spans="1:18">
       <c r="A380" t="s">
         <v>205</v>
       </c>
@@ -82510,7 +82509,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="381" spans="1:18" hidden="1">
+    <row r="381" spans="1:18">
       <c r="A381" t="s">
         <v>205</v>
       </c>
@@ -82557,7 +82556,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="382" spans="1:18" hidden="1">
+    <row r="382" spans="1:18">
       <c r="A382" t="s">
         <v>205</v>
       </c>
@@ -82604,7 +82603,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="383" spans="1:18" hidden="1">
+    <row r="383" spans="1:18">
       <c r="A383" t="s">
         <v>205</v>
       </c>
@@ -82651,7 +82650,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="384" spans="1:18" hidden="1">
+    <row r="384" spans="1:18">
       <c r="A384" t="s">
         <v>205</v>
       </c>
@@ -82698,7 +82697,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="385" spans="1:18" hidden="1">
+    <row r="385" spans="1:18">
       <c r="A385" t="s">
         <v>205</v>
       </c>
@@ -82745,7 +82744,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="386" spans="1:18" hidden="1">
+    <row r="386" spans="1:18">
       <c r="A386" t="s">
         <v>205</v>
       </c>
@@ -82792,7 +82791,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="387" spans="1:18" hidden="1">
+    <row r="387" spans="1:18">
       <c r="A387" t="s">
         <v>205</v>
       </c>
@@ -82839,7 +82838,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="388" spans="1:18" hidden="1">
+    <row r="388" spans="1:18">
       <c r="A388" t="s">
         <v>205</v>
       </c>
@@ -82886,7 +82885,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="389" spans="1:18" hidden="1">
+    <row r="389" spans="1:18">
       <c r="A389" t="s">
         <v>205</v>
       </c>
@@ -82933,7 +82932,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="390" spans="1:18" hidden="1">
+    <row r="390" spans="1:18">
       <c r="A390" t="s">
         <v>205</v>
       </c>
@@ -82980,7 +82979,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="391" spans="1:18" hidden="1">
+    <row r="391" spans="1:18">
       <c r="A391" t="s">
         <v>205</v>
       </c>
@@ -83027,7 +83026,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="392" spans="1:18" hidden="1">
+    <row r="392" spans="1:18">
       <c r="A392" t="s">
         <v>205</v>
       </c>
@@ -83074,7 +83073,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="393" spans="1:18" hidden="1">
+    <row r="393" spans="1:18">
       <c r="A393" t="s">
         <v>205</v>
       </c>
@@ -83121,7 +83120,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="394" spans="1:18" hidden="1">
+    <row r="394" spans="1:18">
       <c r="A394" t="s">
         <v>205</v>
       </c>
@@ -83168,7 +83167,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="395" spans="1:18" hidden="1">
+    <row r="395" spans="1:18">
       <c r="A395" t="s">
         <v>205</v>
       </c>
@@ -83215,7 +83214,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="396" spans="1:18" hidden="1">
+    <row r="396" spans="1:18">
       <c r="A396" t="s">
         <v>205</v>
       </c>
@@ -83262,7 +83261,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="397" spans="1:18" hidden="1">
+    <row r="397" spans="1:18">
       <c r="A397" t="s">
         <v>205</v>
       </c>
@@ -83309,7 +83308,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="398" spans="1:18" hidden="1">
+    <row r="398" spans="1:18">
       <c r="A398" t="s">
         <v>205</v>
       </c>
@@ -83362,7 +83361,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="399" spans="1:18" hidden="1">
+    <row r="399" spans="1:18">
       <c r="A399" t="s">
         <v>205</v>
       </c>
@@ -83409,7 +83408,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="400" spans="1:18" hidden="1">
+    <row r="400" spans="1:18">
       <c r="A400" t="s">
         <v>205</v>
       </c>
@@ -83456,7 +83455,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="401" spans="1:18" hidden="1">
+    <row r="401" spans="1:18">
       <c r="A401" t="s">
         <v>205</v>
       </c>
@@ -83503,7 +83502,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="402" spans="1:18" hidden="1">
+    <row r="402" spans="1:18">
       <c r="A402" t="s">
         <v>205</v>
       </c>
@@ -83550,7 +83549,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="403" spans="1:18" hidden="1">
+    <row r="403" spans="1:18">
       <c r="A403" t="s">
         <v>205</v>
       </c>
@@ -83600,7 +83599,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="404" spans="1:18" hidden="1">
+    <row r="404" spans="1:18">
       <c r="A404" t="s">
         <v>205</v>
       </c>
@@ -83650,7 +83649,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="405" spans="1:18" hidden="1">
+    <row r="405" spans="1:18">
       <c r="A405" t="s">
         <v>205</v>
       </c>
@@ -83700,7 +83699,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="406" spans="1:18" hidden="1">
+    <row r="406" spans="1:18">
       <c r="A406" t="s">
         <v>205</v>
       </c>
@@ -83747,7 +83746,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="407" spans="1:18" hidden="1">
+    <row r="407" spans="1:18">
       <c r="A407" t="s">
         <v>205</v>
       </c>
@@ -83794,7 +83793,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="408" spans="1:18" hidden="1">
+    <row r="408" spans="1:18">
       <c r="A408" t="s">
         <v>205</v>
       </c>
@@ -83841,7 +83840,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="409" spans="1:18" hidden="1">
+    <row r="409" spans="1:18">
       <c r="A409" t="s">
         <v>205</v>
       </c>
@@ -83891,7 +83890,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="410" spans="1:18" hidden="1">
+    <row r="410" spans="1:18">
       <c r="A410" t="s">
         <v>205</v>
       </c>
@@ -83938,7 +83937,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="411" spans="1:18" hidden="1">
+    <row r="411" spans="1:18">
       <c r="A411" t="s">
         <v>205</v>
       </c>
@@ -83985,7 +83984,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="412" spans="1:18" hidden="1">
+    <row r="412" spans="1:18">
       <c r="A412" t="s">
         <v>205</v>
       </c>
@@ -84032,7 +84031,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="413" spans="1:18" hidden="1">
+    <row r="413" spans="1:18">
       <c r="A413" t="s">
         <v>205</v>
       </c>
@@ -84079,7 +84078,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="414" spans="1:18" hidden="1">
+    <row r="414" spans="1:18">
       <c r="A414" t="s">
         <v>205</v>
       </c>
@@ -84126,7 +84125,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="415" spans="1:18" hidden="1">
+    <row r="415" spans="1:18">
       <c r="A415" t="s">
         <v>205</v>
       </c>
@@ -84173,7 +84172,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="416" spans="1:18" hidden="1">
+    <row r="416" spans="1:18">
       <c r="A416" t="s">
         <v>205</v>
       </c>
@@ -84220,7 +84219,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="417" spans="1:18" hidden="1">
+    <row r="417" spans="1:18">
       <c r="A417" t="s">
         <v>205</v>
       </c>
@@ -84268,14 +84267,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X417" xr:uid="{650C6DC7-E293-444D-8EA8-E55F354E543B}">
-    <filterColumn colId="13">
-      <filters>
-        <filter val="Freshwater"/>
-        <filter val="Freshwater_Anadromous"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:X417" xr:uid="{650C6DC7-E293-444D-8EA8-E55F354E543B}"/>
   <hyperlinks>
     <hyperlink ref="T146" r:id="rId1" display="https://www.fws.gov/species/lake-trout-salvelinus-namaycush" xr:uid="{BFD378E1-6E4A-A147-987F-A79AE64C1DEB}"/>
     <hyperlink ref="T236" r:id="rId2" display="https://www.britannica.com/animal/wolffish" xr:uid="{A06C78E2-E9D9-FB47-8D13-DADA11CE923B}"/>
